--- a/docs/技術仕様書.xlsx
+++ b/docs/技術仕様書.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="163">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="174">
   <si>
     <t>1. システム概要・技術基盤</t>
   </si>
@@ -192,6 +192,15 @@
     <t>主担当キャスト（売上最大。CSV表示用）</t>
   </si>
   <si>
+    <t>tableCasts</t>
+  </si>
+  <si>
+    <t>string[]</t>
+  </si>
+  <si>
+    <t>卓バックの受取キャスト（複数なら頭割り）</t>
+  </si>
+  <si>
     <t>completedAt</t>
   </si>
   <si>
@@ -225,7 +234,7 @@
     <t>priceExTax</t>
   </si>
   <si>
-    <t>税抜単価</t>
+    <t>単価（税込モード時はその額が最終価格）</t>
   </si>
   <si>
     <t>qty</t>
@@ -237,7 +246,13 @@
     <t>cast</t>
   </si>
   <si>
-    <t>担当キャスト名（空文字＝未設定）</t>
+    <t>キャストドリンクのドリンクバック用担当（空=未設定）</t>
+  </si>
+  <si>
+    <t>category</t>
+  </si>
+  <si>
+    <t>カテゴリ（キャストドリンク判定等。フリー入力は"フリー入力"）</t>
   </si>
   <si>
     <t>isToday</t>
@@ -273,6 +288,15 @@
     <t>キャスト。sortOrder昇順。注文画面の担当選択肢</t>
   </si>
   <si>
+    <t>tables（席・未会計注文）</t>
+  </si>
+  <si>
+    <t>name/solo/tableCasts/items/createdAt/updatedAt</t>
+  </si>
+  <si>
+    <t>ドキュメントID＝席ID。tableCastsは卓の担当(複数可)。注文操作で保存。リロード復元・端末間共有。会計でitems空に</t>
+  </si>
+  <si>
     <t>settings/fees</t>
   </si>
   <si>
@@ -285,19 +309,19 @@
     <t>settings/back</t>
   </si>
   <si>
-    <t>rate</t>
-  </si>
-  <si>
-    <t>バック率（0.30=30%）</t>
-  </si>
-  <si>
-    <t>※注意</t>
-  </si>
-  <si>
-    <t>席・未会計注文</t>
-  </si>
-  <si>
-    <t>Firestore非保存（端末メモリのみ）。リロードで消える</t>
+    <t>rate/drinkRate</t>
+  </si>
+  <si>
+    <t>卓バック率・キャストドリンクバック率（0.10=10%）</t>
+  </si>
+  <si>
+    <t>settings/tax</t>
+  </si>
+  <si>
+    <t>rate/mode</t>
+  </si>
+  <si>
+    <t>消費税率と扱い（exclusive=税抜加算 / inclusive=税込・加算なし）</t>
   </si>
   <si>
     <t>3. 認証・権限（Firestoreルール）</t>
@@ -321,6 +345,12 @@
     <t>settings</t>
   </si>
   <si>
+    <t>tables</t>
+  </si>
+  <si>
+    <t>ログイン済み（スタッフも注文を取るため）</t>
+  </si>
+  <si>
     <t>create=ログイン済み（スタッフも会計確定可）/ update・delete=オーナーのみ</t>
   </si>
   <si>
@@ -351,22 +381,22 @@
     <t>例</t>
   </si>
   <si>
-    <t>消費税(10%)</t>
-  </si>
-  <si>
-    <t>subtotal=Σ(税抜単価×数量) / tax=floor(subtotal×0.1) / total=subtotal+tax（明細は税抜、税は最後に1回・切捨て）</t>
-  </si>
-  <si>
-    <t>税抜545×3 → subtotal1635, tax163, total1798</t>
+    <t>消費税(設定可)</t>
+  </si>
+  <si>
+    <t>calcBill(base,rate,mode)。exclusive: tax=floor(base×rate),total=base+tax / inclusive: tax=0,total=base（加算しない）。base=Σ(priceExTax×数量)</t>
+  </si>
+  <si>
+    <t>税抜545×3→1635/163/1798、 税込599×3→1797(税表示なし)</t>
   </si>
   <si>
     <t>メニュー単価表示</t>
   </si>
   <si>
-    <t>toTaxInc(p)=floor(p×1.1)（お客様向け総額表示）</t>
-  </si>
-  <si>
-    <t>税抜545 → 表示599</t>
+    <t>displayUnit: exclusive=floor(price×(1+rate)) / inclusive=price（登録額そのまま）</t>
+  </si>
+  <si>
+    <t>税抜545→599、 税込599→599</t>
   </si>
   <si>
     <t>決済手数料</t>
@@ -396,22 +426,22 @@
     <t>預10000・total7800 → 釣2200</t>
   </si>
   <si>
-    <t>キャストバック</t>
-  </si>
-  <si>
-    <t>品目ごとにcastへ税抜売上を割当→ castSales=Σ(税抜単価×数量) / back=round(castSales×backRate)。未設定はバック0。</t>
-  </si>
-  <si>
-    <t>さくら税抜3000・率30% → back900</t>
-  </si>
-  <si>
-    <t>バック率の優先</t>
-  </si>
-  <si>
-    <t>settings/back（画面設定）&gt; VITE_BACK_RATE &gt; 既定0.30</t>
-  </si>
-  <si>
-    <t>画面で30%保存 → backRate=0.30</t>
+    <t>卓バック</t>
+  </si>
+  <si>
+    <t>合計 × 卓バック率 を 卓の担当(tableCasts)で頭割り。担当0人は対象外。</t>
+  </si>
+  <si>
+    <t>合計3200×10%=320。担当2名なら160ずつ</t>
+  </si>
+  <si>
+    <t>ドリンクバック</t>
+  </si>
+  <si>
+    <t>category="キャストドリンク"の品目: 料金×ドリンクバック率 を その品目の担当(item.cast)へ上乗せ。</t>
+  </si>
+  <si>
+    <t>キャストドリンク1200×ドリンク率 → りな（卓バックにも料金含む＝二重計上）</t>
   </si>
   <si>
     <t>売上サマリー</t>
@@ -450,13 +480,10 @@
     <t>No</t>
   </si>
   <si>
-    <t>席・未会計注文は端末メモリのみ（Firestore非保存）。リロード/タブ破棄/再起動で開いている伝票が消える。複数端末で共有不可。営業中は会計完了までリロードしない運用が必要。</t>
-  </si>
-  <si>
     <t>取引の取消・返金機能が無い。打ち間違いはオーナーがFirestoreを直接修正。</t>
   </si>
   <si>
-    <t>オフライン耐性が限定的。会計確定時のネット失敗に対する明確なエラー表示が無い。</t>
+    <t>オフライン耐性が限定的。会計確定時のネット失敗に明確なエラー表示が無い。オフライン永続化(persistentLocalCache)未設定。</t>
   </si>
   <si>
     <t>CSVインジェクション対策なし（席名等に =,+,-,@ 開始の文字列でExcel数式化の懸念）。</t>
@@ -469,6 +496,12 @@
   </si>
   <si>
     <t>キャストのリネーム/削除は過去データに遡及しない（取引内は会計時点の名前を保持）。</t>
+  </si>
+  <si>
+    <t>同じ卓を2端末で同時編集した場合は最後の書き込みが優先（小規模運用想定）。</t>
+  </si>
+  <si>
+    <t>※「席・注文がリロードで消える」はtablesコレクションへの永続化で解消済み（オンライン時）。</t>
   </si>
   <si>
     <t>6. 環境変数（.env）</t>
@@ -1032,7 +1065,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D27"/>
+  <dimension ref="A1:D30"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
@@ -1225,10 +1258,10 @@
         <v>58</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>41</v>
+        <v>59</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="15" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -1236,10 +1269,10 @@
         <v>36</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>61</v>
+        <v>41</v>
       </c>
       <c r="D15" s="4" t="s">
         <v>62</v>
@@ -1247,13 +1280,13 @@
     </row>
     <row r="16" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B16" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="B16" s="4" t="s">
+      <c r="C16" s="4" t="s">
         <v>64</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>30</v>
       </c>
       <c r="D16" s="4" t="s">
         <v>65</v>
@@ -1261,16 +1294,16 @@
     </row>
     <row r="17" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>36</v>
+        <v>66</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C17" s="4" t="s">
         <v>30</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="18" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -1278,13 +1311,13 @@
         <v>36</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="19" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -1292,13 +1325,13 @@
         <v>36</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C19" s="4" t="s">
         <v>41</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="20" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -1306,13 +1339,13 @@
         <v>36</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="21" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -1320,13 +1353,13 @@
         <v>36</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="22" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -1334,83 +1367,125 @@
         <v>36</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="23" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>78</v>
+        <v>36</v>
       </c>
       <c r="B23" s="4" t="s">
         <v>79</v>
       </c>
       <c r="C23" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D23" s="4" t="s">
         <v>80</v>
-      </c>
-      <c r="D23" s="4" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="24" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D24" s="4" t="s">
         <v>82</v>
-      </c>
-      <c r="B24" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="C24" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="D24" s="4" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="25" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="C25" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="B25" s="4" t="s">
+      <c r="D25" s="4" t="s">
         <v>86</v>
-      </c>
-      <c r="C25" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="D25" s="4" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="26" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="B26" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="B26" s="4" t="s">
+      <c r="C26" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="D26" s="4" t="s">
         <v>89</v>
-      </c>
-      <c r="C26" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="D26" s="4" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="27" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="B27" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="B27" s="4" t="s">
+      <c r="C27" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="D27" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="C27" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="D27" s="4" t="s">
+    </row>
+    <row r="28" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="4" t="s">
         <v>93</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="D30" s="4" t="s">
+        <v>101</v>
       </c>
     </row>
   </sheetData>
@@ -1424,7 +1499,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -1434,83 +1509,83 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="2" ht="20" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
     </row>
     <row r="3" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
     </row>
     <row r="4" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
     </row>
     <row r="5" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
     </row>
     <row r="6" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="B6" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>102</v>
-      </c>
-      <c r="B8" t="s">
-        <v>103</v>
-      </c>
-      <c r="C8" t="s">
-        <v>36</v>
+      <c r="B7" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="B9" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="C9" t="s">
         <v>36</v>
@@ -1518,12 +1593,23 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="B10" t="s">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="C10" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>116</v>
+      </c>
+      <c r="B11" t="s">
+        <v>117</v>
+      </c>
+      <c r="C11" t="s">
         <v>36</v>
       </c>
     </row>
@@ -1548,7 +1634,7 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -1558,106 +1644,106 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>110</v>
+        <v>120</v>
       </c>
     </row>
     <row r="3" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>112</v>
+        <v>122</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>113</v>
+        <v>123</v>
       </c>
     </row>
     <row r="4" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
     </row>
     <row r="5" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>119</v>
+        <v>129</v>
       </c>
     </row>
     <row r="6" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>122</v>
+        <v>132</v>
       </c>
     </row>
     <row r="7" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>124</v>
+        <v>134</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>125</v>
+        <v>135</v>
       </c>
     </row>
     <row r="8" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>127</v>
+        <v>137</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
     </row>
     <row r="9" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>131</v>
+        <v>141</v>
       </c>
     </row>
     <row r="10" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>132</v>
+        <v>142</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>133</v>
+        <v>143</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>134</v>
+        <v>144</v>
       </c>
     </row>
     <row r="11" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>135</v>
+        <v>145</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>136</v>
+        <v>146</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>36</v>
@@ -1665,21 +1751,21 @@
     </row>
     <row r="12" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>137</v>
+        <v>147</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>139</v>
+        <v>149</v>
       </c>
     </row>
     <row r="13" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>141</v>
+        <v>151</v>
       </c>
       <c r="C13" s="4" t="s">
         <v>36</v>
@@ -1696,7 +1782,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -1705,13 +1791,13 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>142</v>
+        <v>152</v>
       </c>
       <c r="B1" s="1"/>
     </row>
     <row r="2" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>143</v>
+        <v>153</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>2</v>
@@ -1722,7 +1808,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
     </row>
     <row r="4" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -1730,7 +1816,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>145</v>
+        <v>155</v>
       </c>
     </row>
     <row r="5" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -1738,7 +1824,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>146</v>
+        <v>156</v>
       </c>
     </row>
     <row r="6" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -1746,7 +1832,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>147</v>
+        <v>157</v>
       </c>
     </row>
     <row r="7" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -1754,7 +1840,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>148</v>
+        <v>158</v>
       </c>
     </row>
     <row r="8" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -1762,7 +1848,7 @@
         <v>6</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>149</v>
+        <v>159</v>
       </c>
     </row>
     <row r="9" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -1770,7 +1856,15 @@
         <v>7</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>150</v>
+        <v>160</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>161</v>
       </c>
     </row>
   </sheetData>
@@ -1793,13 +1887,13 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>151</v>
+        <v>162</v>
       </c>
       <c r="B1" s="1"/>
     </row>
     <row r="2" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>152</v>
+        <v>163</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>27</v>
@@ -1807,42 +1901,42 @@
     </row>
     <row r="3" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>153</v>
+        <v>164</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>154</v>
+        <v>165</v>
       </c>
     </row>
     <row r="4" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>155</v>
+        <v>166</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>156</v>
+        <v>167</v>
       </c>
     </row>
     <row r="5" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>157</v>
+        <v>168</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>158</v>
+        <v>169</v>
       </c>
     </row>
     <row r="6" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>159</v>
+        <v>170</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>160</v>
+        <v>171</v>
       </c>
     </row>
     <row r="7" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>161</v>
+        <v>172</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>162</v>
+        <v>173</v>
       </c>
     </row>
   </sheetData>

--- a/docs/技術仕様書.xlsx
+++ b/docs/技術仕様書.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="179">
   <si>
     <t>1. システム概要・技術基盤</t>
   </si>
@@ -324,6 +324,15 @@
     <t>消費税率と扱い（exclusive=税抜加算 / inclusive=税込・加算なし）</t>
   </si>
   <si>
+    <t>closures（レジ締め）</t>
+  </si>
+  <si>
+    <t>date/closedAt/totalSales/cash/card/qr/totalFee/totalNet/totalBack/txCount</t>
+  </si>
+  <si>
+    <t>ドキュメントID＝YYYY-MM-DD。存在＝締め済み。締め済み日は会計記録不可。解除はドキュメント削除</t>
+  </si>
+  <si>
     <t>3. 認証・権限（Firestoreルール）</t>
   </si>
   <si>
@@ -349,6 +358,12 @@
   </si>
   <si>
     <t>ログイン済み（スタッフも注文を取るため）</t>
+  </si>
+  <si>
+    <t>closures</t>
+  </si>
+  <si>
+    <t>オーナーのみ（レジ締め・解除）</t>
   </si>
   <si>
     <t>create=ログイン済み（スタッフも会計確定可）/ update・delete=オーナーのみ</t>
@@ -1065,7 +1080,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D30"/>
+  <dimension ref="A1:D31"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
@@ -1488,6 +1503,20 @@
         <v>101</v>
       </c>
     </row>
+    <row r="31" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="D31" s="4" t="s">
+        <v>104</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:D1"/>
@@ -1499,7 +1528,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -1509,20 +1538,20 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="2" ht="20" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
     </row>
     <row r="3" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -1530,10 +1559,10 @@
         <v>83</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
     </row>
     <row r="4" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -1541,62 +1570,62 @@
         <v>87</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
     </row>
     <row r="5" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
     </row>
     <row r="6" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="B6" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="B6" s="4" t="s">
-        <v>106</v>
-      </c>
       <c r="C6" s="4" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
     </row>
     <row r="7" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="B7" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>112</v>
-      </c>
-      <c r="B9" t="s">
-        <v>113</v>
-      </c>
-      <c r="C9" t="s">
-        <v>36</v>
+      <c r="B8" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="B10" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="C10" t="s">
         <v>36</v>
@@ -1604,12 +1633,23 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="B11" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="C11" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>121</v>
+      </c>
+      <c r="B12" t="s">
+        <v>122</v>
+      </c>
+      <c r="C12" t="s">
         <v>36</v>
       </c>
     </row>
@@ -1634,7 +1674,7 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -1644,106 +1684,106 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
     </row>
     <row r="3" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
     </row>
     <row r="4" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
     </row>
     <row r="5" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
     </row>
     <row r="6" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
     </row>
     <row r="7" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
     </row>
     <row r="8" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
     </row>
     <row r="9" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
     </row>
     <row r="10" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
     </row>
     <row r="11" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>36</v>
@@ -1751,21 +1791,21 @@
     </row>
     <row r="12" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
     </row>
     <row r="13" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="C13" s="4" t="s">
         <v>36</v>
@@ -1791,13 +1831,13 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="B1" s="1"/>
     </row>
     <row r="2" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>2</v>
@@ -1808,7 +1848,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
     </row>
     <row r="4" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -1816,7 +1856,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
     </row>
     <row r="5" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -1824,7 +1864,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
     </row>
     <row r="6" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -1832,7 +1872,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
     </row>
     <row r="7" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -1840,7 +1880,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
     </row>
     <row r="8" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -1848,7 +1888,7 @@
         <v>6</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
     </row>
     <row r="9" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -1856,7 +1896,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
     </row>
     <row r="10" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -1864,7 +1904,7 @@
         <v>85</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
     </row>
   </sheetData>
@@ -1887,13 +1927,13 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="B1" s="1"/>
     </row>
     <row r="2" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>27</v>
@@ -1901,42 +1941,42 @@
     </row>
     <row r="3" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
     </row>
     <row r="4" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
     </row>
     <row r="5" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
     </row>
     <row r="6" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
     </row>
     <row r="7" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
     </row>
   </sheetData>

--- a/docs/技術仕様書.xlsx
+++ b/docs/技術仕様書.xlsx
@@ -456,7 +456,7 @@
     <t>category="キャストドリンク"の品目: 料金×ドリンクバック率 を その品目の担当(item.cast)へ上乗せ。</t>
   </si>
   <si>
-    <t>キャストドリンク1200×ドリンク率 → りな（卓バックにも料金含む＝二重計上）</t>
+    <t>キャストドリンク1200×ドリンク率 → ゆう子（卓バックにも料金含む＝二重計上）</t>
   </si>
   <si>
     <t>売上サマリー</t>
